--- a/data/original/freework01.xlsx
+++ b/data/original/freework01.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
-  <si>
-    <t>筛选条件： 发起时间：2025-07-01 到 2025-08-01 类型：请假 状态：全部 统计：共 52 条审批（编号相同的审批单据计算为一条）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="425">
+  <si>
+    <t>筛选条件： 发起时间：2025-07-27 到 2025-09-02 类型：请假 状态：全部 统计：共 48 条审批（编号相同的审批单据计算为一条）</t>
   </si>
   <si>
     <t>申请编号</t>
@@ -127,16 +127,575 @@
     <t>备注</t>
   </si>
   <si>
-    <t>202507020041</t>
+    <t>202508010002</t>
   </si>
   <si>
     <t>请假</t>
   </si>
   <si>
+    <t>已同意</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>7fe5g917</t>
+  </si>
+  <si>
+    <t>张梓正</t>
+  </si>
+  <si>
+    <t>产品中心/AIO开发部</t>
+  </si>
+  <si>
+    <t>54744g6c6edgb9cf</t>
+  </si>
+  <si>
+    <t>石丁哲;雷继彬</t>
+  </si>
+  <si>
+    <t>张梓正|发起审批|2025-08-01 09:11:00;石丁哲|同意|2025-08-01 18:44:50;雷继彬|同意|2025-08-01 19:56:17</t>
+  </si>
+  <si>
+    <t>10h45m18.207s</t>
+  </si>
+  <si>
+    <t>2025年08月01日 09:10</t>
+  </si>
+  <si>
+    <t>事假</t>
+  </si>
+  <si>
+    <t>2025年08月01日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月01日 下午</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>家里有事</t>
+  </si>
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>202507300001</t>
+  </si>
+  <si>
+    <t>张梓正|发起审批|2025-07-30 08:11:32;石丁哲|同意|2025-07-30 08:42:54;雷继彬|同意|2025-07-30 08:44:11</t>
+  </si>
+  <si>
+    <t>32m39.391s</t>
+  </si>
+  <si>
+    <t>2025年07月30日 08:11</t>
+  </si>
+  <si>
+    <t>2025年07月30日 上午</t>
+  </si>
+  <si>
+    <t>2025年07月31日 下午</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>202507310031</t>
+  </si>
+  <si>
+    <t>81cgb8bc</t>
+  </si>
+  <si>
+    <t>何升绘</t>
+  </si>
+  <si>
+    <t>供应链管理部</t>
+  </si>
+  <si>
+    <t>a4883fa6f6gc35e4</t>
+  </si>
+  <si>
+    <t>陈虞涛</t>
+  </si>
+  <si>
+    <t>陈虞涛;李萍</t>
+  </si>
+  <si>
+    <t>何升绘|发起审批|2025-07-31 18:49:04;陈虞涛|同意|2025-08-09 14:05:11;李萍|同意|2025-08-10 20:12:50</t>
+  </si>
+  <si>
+    <t>241h23m46.712s</t>
+  </si>
+  <si>
+    <t>2025年07月31日 18:34</t>
+  </si>
+  <si>
+    <t>2025年08月05日 下午</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>个人私事处理：共3天，调休1天，请假2天</t>
+  </si>
+  <si>
+    <t>202507310008</t>
+  </si>
+  <si>
+    <t>b3d153g3</t>
+  </si>
+  <si>
+    <t>朱金凯</t>
+  </si>
+  <si>
+    <t>售后服务部</t>
+  </si>
+  <si>
+    <t>gdadd4ge53d74c67</t>
+  </si>
+  <si>
+    <t>张成林</t>
+  </si>
+  <si>
+    <t>朱金凯|发起审批|2025-07-31 10:19:57;张成林|同意|2025-07-31 13:33:46</t>
+  </si>
+  <si>
+    <t>3h13m48.839s</t>
+  </si>
+  <si>
+    <t>2025年07月31日 10:18</t>
+  </si>
+  <si>
+    <t>病假</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>身体不舒服，阳的症状</t>
+  </si>
+  <si>
+    <t>202507310029</t>
+  </si>
+  <si>
     <t>已撤回</t>
   </si>
   <si>
-    <t/>
+    <t>c5ddab8a</t>
+  </si>
+  <si>
+    <t>林明山</t>
+  </si>
+  <si>
+    <t>产品中心/系统开发部</t>
+  </si>
+  <si>
+    <t>32114e27ega71f85</t>
+  </si>
+  <si>
+    <t>朱显斌</t>
+  </si>
+  <si>
+    <t>林明山|发起审批|2025-07-31 17:51:21</t>
+  </si>
+  <si>
+    <t>2m42.112s</t>
+  </si>
+  <si>
+    <t>2025年07月31日 17:50</t>
+  </si>
+  <si>
+    <t>调休</t>
+  </si>
+  <si>
+    <t>家里有事，调休半天</t>
+  </si>
+  <si>
+    <t>202507280006</t>
+  </si>
+  <si>
+    <t>cafg5ac6</t>
+  </si>
+  <si>
+    <t>陈妍</t>
+  </si>
+  <si>
+    <t>综合保障中心/行政部</t>
+  </si>
+  <si>
+    <t>436fee53c83eb4gf</t>
+  </si>
+  <si>
+    <t>尹娜</t>
+  </si>
+  <si>
+    <t>尹娜;李萍</t>
+  </si>
+  <si>
+    <t>陈妍|发起审批|2025-07-28 09:44:48;尹娜|同意|2025-07-28 10:47:52;李萍|同意|2025-07-28 10:53:55</t>
+  </si>
+  <si>
+    <t>1h9m6.711s</t>
+  </si>
+  <si>
+    <t>2025年07月28日 09:40</t>
+  </si>
+  <si>
+    <t>2025年07月29日 上午</t>
+  </si>
+  <si>
+    <t>周二上午复查，中午赶回。</t>
+  </si>
+  <si>
+    <t>202507310016</t>
+  </si>
+  <si>
+    <t>9a282a5e</t>
+  </si>
+  <si>
+    <t>朱泽利</t>
+  </si>
+  <si>
+    <t>石丁哲</t>
+  </si>
+  <si>
+    <t>朱泽利|发起审批|2025-07-31 14:03:14;石丁哲|同意|2025-08-01 09:14:44;雷继彬|同意|2025-08-01 13:54:14</t>
+  </si>
+  <si>
+    <t>23h51m0.315s</t>
+  </si>
+  <si>
+    <t>2025年08月01日 08:30</t>
+  </si>
+  <si>
+    <t>调休，由加班时间调休到2025年8月1日</t>
+  </si>
+  <si>
+    <t>202507280001</t>
+  </si>
+  <si>
+    <t>bc269d6g</t>
+  </si>
+  <si>
+    <t>何佳兴</t>
+  </si>
+  <si>
+    <t>林明山;朱显斌;雷继彬</t>
+  </si>
+  <si>
+    <t>何佳兴|发起审批|2025-07-28 00:37:50;林明山|同意|2025-07-28 08:10:23;朱显斌|同意|2025-07-28 08:24:46;雷继彬|同意|2025-07-29 08:39:17</t>
+  </si>
+  <si>
+    <t>32h1m27.509s</t>
+  </si>
+  <si>
+    <t>2025年07月28日 08:30</t>
+  </si>
+  <si>
+    <t>2025年07月28日 上午</t>
+  </si>
+  <si>
+    <t>2025年07月28日 下午</t>
+  </si>
+  <si>
+    <t>各位领导好，周六夜里肠胃炎症状有些严重，虽有药物控制，但周日还是腹泻了一整天，胃里存不下东西，现在特别乏力虚弱，周一申请调休一天，望领导批准。</t>
+  </si>
+  <si>
+    <t>202508010018</t>
+  </si>
+  <si>
+    <t>陈妍|发起审批|2025-08-01 14:22:56;尹娜|同意|2025-08-04 14:43:04;李萍|同意|2025-08-05 13:57:44</t>
+  </si>
+  <si>
+    <t>95h34m47.642s</t>
+  </si>
+  <si>
+    <t>2025年08月01日 14:23</t>
+  </si>
+  <si>
+    <t>2025年08月04日 上午</t>
+  </si>
+  <si>
+    <t>家里有事，周一上午请假半天。</t>
+  </si>
+  <si>
+    <t>202508010028</t>
+  </si>
+  <si>
+    <t>c349dfcc</t>
+  </si>
+  <si>
+    <t>陈之东</t>
+  </si>
+  <si>
+    <t>陈之东|发起审批|2025-08-01 17:05:26;林明山|同意|2025-08-02 16:47:16;朱显斌|同意|2025-08-02 17:03:46;雷继彬|同意|2025-08-02 17:09:20</t>
+  </si>
+  <si>
+    <t>24h3m53.861s</t>
+  </si>
+  <si>
+    <t>2025年08月04日 08:30</t>
+  </si>
+  <si>
+    <t>2025年08月04日 下午</t>
+  </si>
+  <si>
+    <t>请假回家一趟</t>
+  </si>
+  <si>
+    <t>202508020002</t>
+  </si>
+  <si>
+    <t>dad88d24</t>
+  </si>
+  <si>
+    <t>桂治国</t>
+  </si>
+  <si>
+    <t>朱显斌;雷继彬;李萍</t>
+  </si>
+  <si>
+    <t>桂治国|发起审批|2025-08-02 08:20:36;朱显斌|同意|2025-08-02 09:05:00;雷继彬|同意|2025-08-02 14:40:11;李萍|同意|2025-08-02 17:42:39</t>
+  </si>
+  <si>
+    <t>9h22m3.135s</t>
+  </si>
+  <si>
+    <t>2025年08月02日 08:19</t>
+  </si>
+  <si>
+    <t>2025年08月06日 下午</t>
+  </si>
+  <si>
+    <t>家属手术，需要陪护。</t>
+  </si>
+  <si>
+    <t>202508070002</t>
+  </si>
+  <si>
+    <t>何佳兴|发起审批|2025-08-07 08:37:02;林明山|同意|2025-08-07 08:46:49;朱显斌|同意|2025-08-07 14:03:26;雷继彬|同意|2025-08-07 14:08:29</t>
+  </si>
+  <si>
+    <t>5h31m27.966s</t>
+  </si>
+  <si>
+    <t>2025年08月07日 08:33</t>
+  </si>
+  <si>
+    <t>2025年08月07日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月07日 下午</t>
+  </si>
+  <si>
+    <t>肠炎发作伴随高烧38.6度，申请调休一天 ，去医院检查，望领导批准</t>
+  </si>
+  <si>
+    <t>202508040001</t>
+  </si>
+  <si>
+    <t>fb7adb73</t>
+  </si>
+  <si>
+    <t>梁梅</t>
+  </si>
+  <si>
+    <t>制造中心/仓储物流部</t>
+  </si>
+  <si>
+    <t>aceg73d6d23cdebc</t>
+  </si>
+  <si>
+    <t>张健宁</t>
+  </si>
+  <si>
+    <t>张健宁;杜鸣;石启军</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-08-04 07:20:46;张健宁|同意|2025-08-04 15:05:41;杜鸣|同意|2025-08-04 16:32:10;石启军|同意|2025-08-04 16:38:56</t>
+  </si>
+  <si>
+    <t>9h18m9.418s</t>
+  </si>
+  <si>
+    <t>2025年08月04日 07:13</t>
+  </si>
+  <si>
+    <t>婆婆去世，处理后事</t>
+  </si>
+  <si>
+    <t>202508070004</t>
+  </si>
+  <si>
+    <t>f5b6g99b</t>
+  </si>
+  <si>
+    <t>刘伟豪</t>
+  </si>
+  <si>
+    <t>刘伟豪|发起审批|2025-08-07 08:57:05;石丁哲|同意|2025-08-07 09:10:25;雷继彬|同意|2025-08-07 10:05:04</t>
+  </si>
+  <si>
+    <t>1h7m59.566s</t>
+  </si>
+  <si>
+    <t>2025年08月07日 08:56</t>
+  </si>
+  <si>
+    <t>身体不适</t>
+  </si>
+  <si>
+    <t>202508060039</t>
+  </si>
+  <si>
+    <t>9e569f6b</t>
+  </si>
+  <si>
+    <t>王亮</t>
+  </si>
+  <si>
+    <t>营销中心</t>
+  </si>
+  <si>
+    <t>7a8bfd7e691a49fe</t>
+  </si>
+  <si>
+    <t>罗训强</t>
+  </si>
+  <si>
+    <t>王亮|发起审批|2025-08-06 15:17:28;罗训强|同意|2025-08-06 19:43:08</t>
+  </si>
+  <si>
+    <t>4h25m40.349s</t>
+  </si>
+  <si>
+    <t>2025年08月11日 15:16</t>
+  </si>
+  <si>
+    <t>2025年08月11日 下午</t>
+  </si>
+  <si>
+    <t>2025年08月15日 下午</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>个人事假</t>
+  </si>
+  <si>
+    <t>202508050004</t>
+  </si>
+  <si>
+    <t>c617e425</t>
+  </si>
+  <si>
+    <t>李淑娜</t>
+  </si>
+  <si>
+    <t>桂治国;朱显斌;雷继彬</t>
+  </si>
+  <si>
+    <t>李淑娜|发起审批|2025-08-05 08:13:50;桂治国|同意|2025-08-05 08:40:03;朱显斌|同意|2025-08-05 08:43:37;雷继彬|同意|2025-08-05 08:44:44</t>
+  </si>
+  <si>
+    <t>30m54.584s</t>
+  </si>
+  <si>
+    <t>2025年08月05日 08:00</t>
+  </si>
+  <si>
+    <t>送我妈去高铁站</t>
+  </si>
+  <si>
+    <t>202508070042</t>
+  </si>
+  <si>
+    <t>a53f348a</t>
+  </si>
+  <si>
+    <t>李萍;罗训强</t>
+  </si>
+  <si>
+    <t>尹娜|发起审批|2025-08-07 22:58:55;李萍|同意|2025-08-08 08:20:03;罗训强|同意|2025-08-08 08:23:27</t>
+  </si>
+  <si>
+    <t>9h24m31.436s</t>
+  </si>
+  <si>
+    <t>2025年08月07日 22:56</t>
+  </si>
+  <si>
+    <t>2025年08月09日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月09日 下午</t>
+  </si>
+  <si>
+    <t>因个人事情，去安徽蚌埠，往返时间较长，提前周六前往，请假一天。</t>
+  </si>
+  <si>
+    <t>202508080010</t>
+  </si>
+  <si>
+    <t>994g1dd6</t>
+  </si>
+  <si>
+    <t>周天</t>
+  </si>
+  <si>
+    <t>周天|发起审批|2025-08-08 10:51:29;张成林|同意|2025-08-08 14:23:47</t>
+  </si>
+  <si>
+    <t>3h32m17.794s</t>
+  </si>
+  <si>
+    <t>2025年08月09日 08:30</t>
+  </si>
+  <si>
+    <t>6.15调休到8.9</t>
+  </si>
+  <si>
+    <t>202508080035</t>
+  </si>
+  <si>
+    <t>朱泽利|发起审批|2025-08-08 16:25:23;石丁哲|同意|2025-08-09 08:55:30;雷继彬|同意|2025-08-09 14:40:47</t>
+  </si>
+  <si>
+    <t>22h15m23.978s</t>
+  </si>
+  <si>
+    <t>调休，由加班时间调休到2025年8月9日</t>
+  </si>
+  <si>
+    <t>202508080002</t>
+  </si>
+  <si>
+    <t>462a1a3e</t>
+  </si>
+  <si>
+    <t>李运动</t>
+  </si>
+  <si>
+    <t>李运动|发起审批|2025-08-08 08:43:46;张健宁|同意|2025-08-08 11:12:39;杜鸣|同意|2025-08-08 11:17:04;石启军|同意|2025-08-08 11:30:51</t>
+  </si>
+  <si>
+    <t>2h47m5.053s</t>
+  </si>
+  <si>
+    <t>2025年08月08日 08:30</t>
+  </si>
+  <si>
+    <t>2025年08月08日 上午</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+有事，已加班，故2025-08-08上午调休半天，望领导批准！</t>
+  </si>
+  <si>
+    <t>202508080041</t>
   </si>
   <si>
     <t>g5b8a9b8</t>
@@ -151,34 +710,482 @@
     <t>6fae3b572egdecef</t>
   </si>
   <si>
-    <t>周哲敏|发起审批|2025-07-02 20:34:33</t>
-  </si>
-  <si>
-    <t>16.662s</t>
-  </si>
-  <si>
-    <t>2025年07月02日 20:30</t>
-  </si>
-  <si>
-    <t>事假</t>
-  </si>
-  <si>
-    <t>2025年07月03日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月03日 下午</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>家里人动小手术</t>
-  </si>
-  <si>
-    <t>天</t>
-  </si>
-  <si>
-    <t>202507120001</t>
+    <t>周哲敏|发起审批|2025-08-08 16:51:48;李萍|同意|2025-08-08 16:53:10;罗训强|同意|2025-08-08 16:56:45</t>
+  </si>
+  <si>
+    <t>4m56.351s</t>
+  </si>
+  <si>
+    <t>2025年08月08日 16:30</t>
+  </si>
+  <si>
+    <t>家中小孩有事要处理</t>
+  </si>
+  <si>
+    <t>202508130036</t>
+  </si>
+  <si>
+    <t>朱显斌;雷继彬</t>
+  </si>
+  <si>
+    <t>桂治国|发起审批|2025-08-13 21:29:40;朱显斌|同意|2025-08-14 08:51:07;雷继彬|同意|2025-08-14 08:55:11</t>
+  </si>
+  <si>
+    <t>11h25m31.279s</t>
+  </si>
+  <si>
+    <t>2025年08月13日 21:28</t>
+  </si>
+  <si>
+    <t>2025年08月14日 上午</t>
+  </si>
+  <si>
+    <t>家中有事情需要处理。</t>
+  </si>
+  <si>
+    <t>202508130028</t>
+  </si>
+  <si>
+    <t>86f6cb4f</t>
+  </si>
+  <si>
+    <t>杜鸣;罗训强;周哲敏;罗训强</t>
+  </si>
+  <si>
+    <t>张健宁|发起审批|2025-08-13 17:51:07;杜鸣|同意|2025-08-13 21:23:01;罗训强|前加签|2025-08-13 22:36:30;周哲敏|同意|2025-08-14 16:46:13;罗训强|同意|2025-08-14 16:54:50</t>
+  </si>
+  <si>
+    <t>23h3m43.702s</t>
+  </si>
+  <si>
+    <t>2025年08月13日 17:49</t>
+  </si>
+  <si>
+    <t>2025年08月19日 下午</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>回老家处理孩子上学事宜。扣除星期六，星期天。实际调休申请4天。
+请领导批示。</t>
+  </si>
+  <si>
+    <t>202508100002</t>
+  </si>
+  <si>
+    <t>849773g8</t>
+  </si>
+  <si>
+    <t>闫亚东</t>
+  </si>
+  <si>
+    <t>闫亚东|发起审批|2025-08-10 14:40:40;桂治国|同意|2025-08-10 17:56:06;朱显斌|同意|2025-08-10 21:16:42;雷继彬|同意|2025-08-10 22:09:22</t>
+  </si>
+  <si>
+    <t>7h28m41.574s</t>
+  </si>
+  <si>
+    <t>2025年08月10日 14:40</t>
+  </si>
+  <si>
+    <t>2025年08月18日 上午</t>
+  </si>
+  <si>
+    <t>拍摄婚纱照需要调休两天</t>
+  </si>
+  <si>
+    <t>202508090023</t>
+  </si>
+  <si>
+    <t>964g15b2</t>
+  </si>
+  <si>
+    <t>张世丽</t>
+  </si>
+  <si>
+    <t>信息和品宣部</t>
+  </si>
+  <si>
+    <t>39cd39a3aa886c91</t>
+  </si>
+  <si>
+    <t>杜以烽</t>
+  </si>
+  <si>
+    <t>杜以烽;罗训强</t>
+  </si>
+  <si>
+    <t>张世丽|发起审批|2025-08-09 16:53:32;杜以烽|同意|2025-08-09 17:51:35;罗训强|同意|2025-08-10 21:49:38</t>
+  </si>
+  <si>
+    <t>28h56m6.225s</t>
+  </si>
+  <si>
+    <t>2025年08月09日 16:51</t>
+  </si>
+  <si>
+    <t>身体很不适，在家调整</t>
+  </si>
+  <si>
+    <t>202508100008</t>
+  </si>
+  <si>
+    <t>桂治国|发起审批|2025-08-10 18:46:57;朱显斌|同意|2025-08-10 18:47:11;雷继彬|同意|"节哀顺变" |2025-08-10 22:09:35;李萍|同意|2025-08-12 08:49:06</t>
+  </si>
+  <si>
+    <t>38h2m9.565s</t>
+  </si>
+  <si>
+    <t>2025年08月10日 18:45</t>
+  </si>
+  <si>
+    <t>2025年08月11日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月13日 下午</t>
+  </si>
+  <si>
+    <t>父亲去世，丧假。</t>
+  </si>
+  <si>
+    <t>202508140052</t>
+  </si>
+  <si>
+    <t>c252fg26</t>
+  </si>
+  <si>
+    <t>张喆</t>
+  </si>
+  <si>
+    <t>张喆|发起审批|2025-08-14 19:58:20;林明山|同意|2025-08-14 20:00:25;朱显斌|同意|2025-08-14 20:16:19;雷继彬|同意|2025-08-15 05:00:50</t>
+  </si>
+  <si>
+    <t>9h2m30.89s</t>
+  </si>
+  <si>
+    <t>2025年08月14日 19:57</t>
+  </si>
+  <si>
+    <t>2025年08月15日 上午</t>
+  </si>
+  <si>
+    <t>医院复查</t>
+  </si>
+  <si>
+    <t>202508140010</t>
+  </si>
+  <si>
+    <t>5e21ef5b</t>
+  </si>
+  <si>
+    <t>李黎</t>
+  </si>
+  <si>
+    <t>质量保证部</t>
+  </si>
+  <si>
+    <t>6g81a528518e967g</t>
+  </si>
+  <si>
+    <t>李锋;张成林</t>
+  </si>
+  <si>
+    <t>李黎|发起审批|2025-08-14 10:18:39;李锋|同意|2025-08-14 10:30:53;张成林|同意|2025-08-14 14:57:05</t>
+  </si>
+  <si>
+    <t>4h38m25.985s</t>
+  </si>
+  <si>
+    <t>2025年08月14日 10:14</t>
+  </si>
+  <si>
+    <t>2025年08月18日 下午</t>
+  </si>
+  <si>
+    <t>事假调休(调休6月22日出差时代电机周末加班)</t>
+  </si>
+  <si>
+    <t>202508180007</t>
+  </si>
+  <si>
+    <t>57b3b516</t>
+  </si>
+  <si>
+    <t>韩荣洋</t>
+  </si>
+  <si>
+    <t>韩荣洋|发起审批|2025-08-18 10:05:58;李锋|同意|"同意" |2025-08-18 22:37:15;张成林|同意|2025-08-19 11:59:11</t>
+  </si>
+  <si>
+    <t>25h53m13.311s</t>
+  </si>
+  <si>
+    <t>2025年08月18日 10:05</t>
+  </si>
+  <si>
+    <t>调休，休息半天</t>
+  </si>
+  <si>
+    <t>202508240004</t>
+  </si>
+  <si>
+    <t>朱金凯|发起审批|2025-08-24 22:18:54;张成林|同意|2025-08-24 23:26:58</t>
+  </si>
+  <si>
+    <t>1h8m4.075s</t>
+  </si>
+  <si>
+    <t>2025年08月24日 22:17</t>
+  </si>
+  <si>
+    <t>2025年08月25日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月25日 下午</t>
+  </si>
+  <si>
+    <t>6.25，8.2，8.24加班，调休一天</t>
+  </si>
+  <si>
+    <t>202508200026</t>
+  </si>
+  <si>
+    <t>2811f751</t>
+  </si>
+  <si>
+    <t>程铤辉</t>
+  </si>
+  <si>
+    <t>程铤辉|发起审批|2025-08-20 16:17:13;张成林|同意|2025-08-20 17:06:27</t>
+  </si>
+  <si>
+    <t>49m14.633s</t>
+  </si>
+  <si>
+    <t>2025年08月22日 08:30</t>
+  </si>
+  <si>
+    <t>2025年08月22日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月23日 下午</t>
+  </si>
+  <si>
+    <t>调休两天回老家一趟办事</t>
+  </si>
+  <si>
+    <t>202508250033</t>
+  </si>
+  <si>
+    <t>周天|发起审批|2025-08-25 22:12:33;张成林|同意|2025-08-26 17:33:12</t>
+  </si>
+  <si>
+    <t>19h20m39.76s</t>
+  </si>
+  <si>
+    <t>2025年08月27日 22:11</t>
+  </si>
+  <si>
+    <t>2025年08月27日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月27日 下午</t>
+  </si>
+  <si>
+    <t>6.21调休到8.27</t>
+  </si>
+  <si>
+    <t>202508260055</t>
+  </si>
+  <si>
+    <t>何佳兴|发起审批|2025-08-26 23:27:40;林明山|同意|2025-08-27 09:25:47;朱显斌|同意|2025-08-27 09:29:49;雷继彬|同意|2025-08-27 10:22:02</t>
+  </si>
+  <si>
+    <t>10h54m22.861s</t>
+  </si>
+  <si>
+    <t>2025年08月27日 08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 到医院复查  另外家里有事   申请调休</t>
+  </si>
+  <si>
+    <t>202508190037</t>
+  </si>
+  <si>
+    <t>5gcg661g</t>
+  </si>
+  <si>
+    <t>丁国涛</t>
+  </si>
+  <si>
+    <t>丁国涛|发起审批|2025-08-19 18:43:34;林明山|同意|2025-08-19 18:44:14;朱显斌|同意|2025-08-19 23:47:12;雷继彬|同意|2025-08-20 07:27:17</t>
+  </si>
+  <si>
+    <t>12h43m43.756s</t>
+  </si>
+  <si>
+    <t>2025年08月20日 08:30</t>
+  </si>
+  <si>
+    <t>2025年08月20日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月20日 下午</t>
+  </si>
+  <si>
+    <t>家中有事，需要调休</t>
+  </si>
+  <si>
+    <t>202508270001</t>
+  </si>
+  <si>
+    <t>丁国涛|发起审批|2025-08-27 07:43:27;林明山|同意|2025-08-27 08:01:17;朱显斌|同意|2025-08-27 08:19:04;雷继彬|同意|2025-08-27 10:22:09</t>
+  </si>
+  <si>
+    <t>2h38m42.829s</t>
+  </si>
+  <si>
+    <t>家中人生病不舒服，陪同就医</t>
+  </si>
+  <si>
+    <t>202508210044</t>
+  </si>
+  <si>
+    <t>d9845775</t>
+  </si>
+  <si>
+    <t>叶旭</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-21 23:13:04;张健宁|同意|2025-08-22 08:36:28;杜鸣|同意|2025-08-22 09:53:30;石启军|同意|2025-08-22 10:51:45</t>
+  </si>
+  <si>
+    <t>11h38m40.671s</t>
+  </si>
+  <si>
+    <t>2025年08月22日 下午</t>
+  </si>
+  <si>
+    <t>202508280012</t>
+  </si>
+  <si>
+    <t>丁国涛|发起审批|2025-08-28 14:01:51;林明山|同意|2025-08-28 18:25:15;朱显斌|同意|2025-08-28 18:35:55;雷继彬|同意|2025-08-28 19:05:41</t>
+  </si>
+  <si>
+    <t>5h3m50.35s</t>
+  </si>
+  <si>
+    <t>2025年08月27日 08:28</t>
+  </si>
+  <si>
+    <t>家中人生病不舒服，陪同就医，事情繁琐，没能按计划下午回公司工作，也忘记提前打调休流程，现在发起调休流程，补调休半天。</t>
+  </si>
+  <si>
+    <t>202508270025</t>
+  </si>
+  <si>
+    <t>李运动|发起审批|2025-08-27 15:20:05;张健宁|同意|2025-08-27 16:02:47;杜鸣|同意|2025-08-27 16:02:56;石启军|同意|2025-08-27 16:14:36</t>
+  </si>
+  <si>
+    <t>54m30.482s</t>
+  </si>
+  <si>
+    <t>2025年08月28日 08:30</t>
+  </si>
+  <si>
+    <t>2025年08月28日 上午</t>
+  </si>
+  <si>
+    <t>2025年08月29日 下午</t>
+  </si>
+  <si>
+    <t>有事，已加班，故2025-8-28/29号调休两天，望领导批准！</t>
+  </si>
+  <si>
+    <t>202508280003</t>
+  </si>
+  <si>
+    <t>刘伟豪|发起审批|2025-08-28 08:59:01;石丁哲|同意|2025-08-28 10:23:49;雷继彬|同意|2025-08-28 13:37:06</t>
+  </si>
+  <si>
+    <t>4h38m5.557s</t>
+  </si>
+  <si>
+    <t>2025年08月28日 08:58</t>
+  </si>
+  <si>
+    <t>2025年08月28日 下午</t>
+  </si>
+  <si>
+    <t>202508270015</t>
+  </si>
+  <si>
+    <t>4c719c87</t>
+  </si>
+  <si>
+    <t>雷继彬;罗训强</t>
+  </si>
+  <si>
+    <t>石丁哲|发起审批|2025-08-27 11:55:57;雷继彬|同意|2025-08-27 11:59:40;罗训强|同意|2025-08-27 12:07:36</t>
+  </si>
+  <si>
+    <t>11m38.819s</t>
+  </si>
+  <si>
+    <t>2025年08月27日 11:55</t>
+  </si>
+  <si>
+    <t>去趟医院</t>
+  </si>
+  <si>
+    <t>202508270037</t>
+  </si>
+  <si>
+    <t>5191d5bg</t>
+  </si>
+  <si>
+    <t>姚明佳</t>
+  </si>
+  <si>
+    <t>张世丽;杜以烽</t>
+  </si>
+  <si>
+    <t>姚明佳|发起审批|2025-08-27 22:53:28;张世丽|同意|2025-08-28 09:13:55;杜以烽|同意|2025-08-28 10:43:53</t>
+  </si>
+  <si>
+    <t>11h50m25.827s</t>
+  </si>
+  <si>
+    <t>家里有事，加班调休</t>
+  </si>
+  <si>
+    <t>202508270002</t>
+  </si>
+  <si>
+    <t>766d8dad</t>
+  </si>
+  <si>
+    <t>杨烜</t>
+  </si>
+  <si>
+    <t>;石丁哲;雷继彬</t>
+  </si>
+  <si>
+    <t>|自动通过|2025-08-27 08:26:59;杨烜|发起审批|2025-08-27 08:26:59;石丁哲|同意|2025-08-27 10:20:20;雷继彬|同意|2025-08-27 10:21:50</t>
+  </si>
+  <si>
+    <t>1h54m51.711s</t>
+  </si>
+  <si>
+    <t>2025年08月27日 08:25</t>
+  </si>
+  <si>
+    <t>生病</t>
+  </si>
+  <si>
+    <t>202508280031</t>
   </si>
   <si>
     <t>eg5gd8ea</t>
@@ -187,1221 +1194,103 @@
     <t>甘金利</t>
   </si>
   <si>
-    <t>售后服务部</t>
-  </si>
-  <si>
-    <t>gdadd4ge53d74c67</t>
-  </si>
-  <si>
-    <t>张成林</t>
-  </si>
-  <si>
-    <t>甘金利|发起审批|2025-07-12 08:28:54</t>
-  </si>
-  <si>
-    <t>28h49m56.87s</t>
-  </si>
-  <si>
-    <t>2025年07月12日 06:22</t>
-  </si>
-  <si>
-    <t>调休</t>
-  </si>
-  <si>
-    <t>2025年07月14日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月18日 下午</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>六月十五   二十二号  二十九号  七月六号  十三号</t>
-  </si>
-  <si>
-    <t>202507020001</t>
-  </si>
-  <si>
-    <t>已同意</t>
-  </si>
-  <si>
-    <t>86f6cb4f</t>
-  </si>
-  <si>
-    <t>张健宁</t>
-  </si>
-  <si>
-    <t>制造中心/仓储物流部</t>
-  </si>
-  <si>
-    <t>aceg73d6d23cdebc</t>
-  </si>
-  <si>
-    <t>杜鸣;罗训强</t>
-  </si>
-  <si>
-    <t>张健宁|发起审批|2025-07-02 04:38:03;杜鸣|同意|2025-07-02 08:14:56;罗训强|同意|2025-07-02 09:30:27</t>
-  </si>
-  <si>
-    <t>4h52m24.24s</t>
-  </si>
-  <si>
-    <t>2025年07月02日 04:36</t>
-  </si>
-  <si>
-    <t>2025年07月02日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月02日 下午</t>
-  </si>
-  <si>
-    <t>孩子中考报志愿，去学校参加家长沟通会</t>
-  </si>
-  <si>
-    <t>202507050002</t>
-  </si>
-  <si>
-    <t>d9845775</t>
-  </si>
-  <si>
-    <t>叶旭</t>
-  </si>
-  <si>
-    <t>张健宁;杜鸣;石启军</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-05 07:46:13;张健宁|同意|2025-07-05 11:00:39;杜鸣|同意|2025-07-05 16:07:28;石启军|同意|2025-07-05 16:21:39</t>
-  </si>
-  <si>
-    <t>8h35m26.463s</t>
-  </si>
-  <si>
-    <t>2025年07月05日 07:45</t>
-  </si>
-  <si>
-    <t>2025年07月05日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月05日 下午</t>
-  </si>
-  <si>
-    <t>202507040018</t>
-  </si>
-  <si>
-    <t>462a1a3e</t>
-  </si>
-  <si>
-    <t>李运动</t>
-  </si>
-  <si>
-    <t>李运动|发起审批|2025-07-04 16:32:59;张健宁|同意|2025-07-04 18:51:35;杜鸣|同意|2025-07-05 08:15:36;石启军|同意|2025-07-05 08:52:13</t>
-  </si>
-  <si>
-    <t>16h19m14.388s</t>
-  </si>
-  <si>
-    <t>2025年07月04日 08:30</t>
-  </si>
-  <si>
-    <t>2025年07月04日 上午</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>有事，已加班，故2025-07-04上午调休半天，望领导批准！</t>
-  </si>
-  <si>
-    <t>202507020042</t>
-  </si>
-  <si>
-    <t>审批中</t>
-  </si>
-  <si>
-    <t>周哲敏|发起审批|2025-07-02 20:36:04</t>
-  </si>
-  <si>
-    <t>李萍</t>
-  </si>
-  <si>
-    <t>家里人动小手术
-（请假调休）</t>
-  </si>
-  <si>
-    <t>202507040008</t>
-  </si>
-  <si>
-    <t>5e21ef5b</t>
-  </si>
-  <si>
-    <t>李黎</t>
-  </si>
-  <si>
-    <t>质量保证部</t>
-  </si>
-  <si>
-    <t>6g81a528518e967g</t>
-  </si>
-  <si>
-    <t>李锋;张成林</t>
-  </si>
-  <si>
-    <t>李黎|发起审批|2025-07-04 13:43:33;李锋|同意|"同意" |2025-07-04 13:53:00;张成林|同意|2025-07-04 18:50:31</t>
-  </si>
-  <si>
-    <t>5h6m58.438s</t>
-  </si>
-  <si>
-    <t>2025年07月07日 08:30</t>
-  </si>
-  <si>
-    <t>2025年07月07日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月07日 下午</t>
-  </si>
-  <si>
-    <t>事假调休(调休6月15日出差加班)</t>
-  </si>
-  <si>
-    <t>202507010021</t>
-  </si>
-  <si>
-    <t>cgb7egag</t>
-  </si>
-  <si>
-    <t>殷四雄</t>
-  </si>
-  <si>
-    <t>殷四雄|发起审批|2025-07-01 15:11:33;李锋|同意|"同意" |2025-07-01 18:17:50;张成林|同意|2025-07-02 19:52:22</t>
-  </si>
-  <si>
-    <t>28h40m49.378s</t>
-  </si>
-  <si>
-    <t>2025年07月01日 15:10</t>
-  </si>
-  <si>
-    <t>累计调休</t>
-  </si>
-  <si>
-    <t>202507070001</t>
-  </si>
-  <si>
-    <t>张健宁|发起审批|2025-07-07 08:03:47;杜鸣|同意|2025-07-07 08:10:18;罗训强|同意|2025-07-07 08:11:40</t>
-  </si>
-  <si>
-    <t>7m53.315s</t>
-  </si>
-  <si>
-    <t>2025年07月07日 08:02</t>
-  </si>
-  <si>
-    <t>上午带孩子去医院看病，下午去学校确认中考志愿填报结果。</t>
-  </si>
-  <si>
-    <t>202507050016</t>
-  </si>
-  <si>
-    <t>b3d153g3</t>
-  </si>
-  <si>
-    <t>朱金凯</t>
-  </si>
-  <si>
-    <t>朱金凯|发起审批|2025-07-05 17:36:09;张成林|同意|2025-07-06 19:31:38</t>
-  </si>
-  <si>
-    <t>25h55m29.893s</t>
-  </si>
-  <si>
-    <t>2025年07月05日 17:35</t>
-  </si>
-  <si>
-    <t>2025年07月08日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月08日 下午</t>
-  </si>
-  <si>
-    <t>6月5日晚上+6月6日凌晨加班，调休到8号，下周二。
-家中有事</t>
-  </si>
-  <si>
-    <t>202507080038</t>
-  </si>
-  <si>
-    <t>ba79bda3</t>
-  </si>
-  <si>
-    <t>吴勇明</t>
-  </si>
-  <si>
-    <t>吴勇明|发起审批|2025-07-08 18:00:38;张成林|同意|2025-07-09 01:16:45</t>
-  </si>
-  <si>
-    <t>7h16m6.838s</t>
-  </si>
-  <si>
-    <t>2025年07月08日 16:30</t>
-  </si>
-  <si>
-    <t>2025年07月09日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月09日 下午</t>
-  </si>
-  <si>
-    <t>调休  5.18调至7.9日 休</t>
-  </si>
-  <si>
-    <t>202507100004</t>
-  </si>
-  <si>
-    <t>819385gf</t>
-  </si>
-  <si>
-    <t>孙润</t>
-  </si>
-  <si>
-    <t>产品中心/系统开发部</t>
-  </si>
-  <si>
-    <t>32114e27ega71f85</t>
-  </si>
-  <si>
-    <t>林明山;朱显斌;雷继彬</t>
-  </si>
-  <si>
-    <t>孙润|发起审批|2025-07-10 10:41:50;林明山|同意|2025-07-10 11:10:27;朱显斌|同意|2025-07-10 11:22:28;雷继彬|同意|2025-07-10 19:42:28</t>
-  </si>
-  <si>
-    <t>9h0m39.15s</t>
-  </si>
-  <si>
-    <t>2025年07月10日 12:00</t>
-  </si>
-  <si>
-    <t>2025年07月10日 下午</t>
-  </si>
-  <si>
-    <t>家里有事，调休半天</t>
-  </si>
-  <si>
-    <t>202507080039</t>
-  </si>
-  <si>
-    <t>4c719c87</t>
-  </si>
-  <si>
-    <t>石丁哲</t>
-  </si>
-  <si>
-    <t>产品中心/AIO开发部</t>
-  </si>
-  <si>
-    <t>54744g6c6edgb9cf</t>
-  </si>
-  <si>
-    <t>雷继彬;罗训强</t>
-  </si>
-  <si>
-    <t>石丁哲|发起审批|2025-07-08 18:16:07;雷继彬|同意|2025-07-08 18:30:39;罗训强|同意|2025-07-08 18:37:02</t>
-  </si>
-  <si>
-    <t>20m55.025s</t>
-  </si>
-  <si>
-    <t>2025年06月28日 08:00</t>
-  </si>
-  <si>
-    <t>2025年06月28日 上午</t>
-  </si>
-  <si>
-    <t>2025年06月28日 下午</t>
-  </si>
-  <si>
-    <t>（补）家里来客人，申请周六调休，调休日期：5.12（周末，吴山镇测试）</t>
-  </si>
-  <si>
-    <t>202507090001</t>
-  </si>
-  <si>
-    <t>c349dfcc</t>
-  </si>
-  <si>
-    <t>陈之东</t>
-  </si>
-  <si>
-    <t>朱显斌</t>
-  </si>
-  <si>
-    <t>陈之东|发起审批|2025-07-09 07:44:10;林明山|同意|2025-07-09 08:31:28;朱显斌|同意|2025-07-09 08:43:08;雷继彬|同意|2025-07-09 12:22:28</t>
-  </si>
-  <si>
-    <t>4h38m19.267s</t>
-  </si>
-  <si>
-    <t>2025年07月09日 08:30</t>
-  </si>
-  <si>
-    <t>发烧  申请调休</t>
-  </si>
-  <si>
-    <t>202507090035</t>
-  </si>
-  <si>
-    <t>f5b6g99b</t>
-  </si>
-  <si>
-    <t>刘伟豪</t>
-  </si>
-  <si>
-    <t>石丁哲;雷继彬</t>
-  </si>
-  <si>
-    <t>刘伟豪|发起审批|2025-07-09 18:23:13;石丁哲|同意|2025-07-09 18:26:06;雷继彬|同意|2025-07-09 18:57:22</t>
-  </si>
-  <si>
-    <t>34m9.692s</t>
-  </si>
-  <si>
-    <t>2025年07月09日 18:14</t>
-  </si>
-  <si>
-    <t>2025年07月10日 上午</t>
-  </si>
-  <si>
-    <t>家里有事</t>
-  </si>
-  <si>
-    <t>202507110024</t>
-  </si>
-  <si>
-    <t>b5ec132g</t>
-  </si>
-  <si>
-    <t>崔普金</t>
-  </si>
-  <si>
-    <t>营销中心</t>
-  </si>
-  <si>
-    <t>7a8bfd7e691a49fe</t>
-  </si>
-  <si>
-    <t>崔普金,罗训强</t>
-  </si>
-  <si>
-    <t>罗训强</t>
-  </si>
-  <si>
-    <t>崔普金|发起审批|2025-07-11 12:10:17;罗训强|同意|2025-07-11 12:13:24</t>
-  </si>
-  <si>
-    <t>3m6.254s</t>
-  </si>
-  <si>
-    <t>2025年07月11日 13:12</t>
-  </si>
-  <si>
-    <t>2025年07月12日 上午</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>回家</t>
-  </si>
-  <si>
-    <t>202507110037</t>
-  </si>
-  <si>
-    <t>eec52f77</t>
-  </si>
-  <si>
-    <t>杜锋</t>
-  </si>
-  <si>
-    <t>杜锋|发起审批|2025-07-11 16:07:04;李锋|同意|2025-07-11 17:01:02;张成林|同意|2025-07-11 20:18:32</t>
-  </si>
-  <si>
-    <t>4h11m28.017s</t>
-  </si>
-  <si>
-    <t>2025年07月12日 08:30</t>
-  </si>
-  <si>
-    <t>2025年07月12日 下午</t>
-  </si>
-  <si>
-    <t>202507120012</t>
-  </si>
-  <si>
-    <t>2811f751</t>
-  </si>
-  <si>
-    <t>程铤辉</t>
-  </si>
-  <si>
-    <t>程铤辉|发起审批|2025-07-12 10:13:50;张成林|同意|2025-07-12 15:39:45</t>
-  </si>
-  <si>
-    <t>5h25m55.592s</t>
-  </si>
-  <si>
-    <t>2025年07月12日 10:11</t>
-  </si>
-  <si>
-    <t>送小孩回老家后根据需要支援合肥或其他区域</t>
-  </si>
-  <si>
-    <t>202507140002</t>
-  </si>
-  <si>
-    <t>吴勇明|发起审批|2025-07-14 02:03:26;张成林|同意|2025-07-14 07:16:55</t>
-  </si>
-  <si>
-    <t>5h13m29.511s</t>
-  </si>
-  <si>
-    <t>2025年07月14日 02:01</t>
-  </si>
-  <si>
-    <t>2025年07月14日 下午</t>
-  </si>
-  <si>
-    <t>调休  5.24 调至7.14日休</t>
-  </si>
-  <si>
-    <t>202507130004</t>
-  </si>
-  <si>
-    <t>张成林;李萍</t>
-  </si>
-  <si>
-    <t>甘金利|发起审批|2025-07-13 13:19:37;张成林|同意|2025-07-13 13:23:12;李萍|同意|2025-07-14 08:41:55</t>
-  </si>
-  <si>
-    <t>19h22m17.89s</t>
-  </si>
-  <si>
-    <t>2025年07月16日 下午</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">六月十五   二十二号  二十九号  </t>
-  </si>
-  <si>
-    <t>202507140001</t>
-  </si>
-  <si>
-    <t>李黎|发起审批|2025-07-14 00:50:34;李锋|同意|2025-07-14 08:50:50;张成林|同意|2025-07-14 15:48:29</t>
-  </si>
-  <si>
-    <t>14h57m54.471s</t>
-  </si>
-  <si>
-    <t>2025年07月14日 08:30</t>
-  </si>
-  <si>
-    <t>出差处理客户车辆问题，返回杭州已是7月14日凌晨，调休一天(7月13日出差加班)</t>
-  </si>
-  <si>
-    <t>202507120035</t>
-  </si>
-  <si>
-    <t>25b69587</t>
-  </si>
-  <si>
-    <t>王进</t>
-  </si>
-  <si>
-    <t>张成林;李萍;周哲敏</t>
-  </si>
-  <si>
-    <t>王进|发起审批|2025-07-12 20:20:31;张成林|同意|2025-07-13 13:12:17;李萍|转交|2025-07-14 08:42:21;周哲敏|同意|2025-07-14 08:56:41</t>
-  </si>
-  <si>
-    <t>36h36m9.904s</t>
-  </si>
-  <si>
-    <t>2025年07月12日 20:15</t>
-  </si>
-  <si>
-    <t>病假</t>
-  </si>
-  <si>
-    <t>连续几天晚上加班，在7月11日晚上加班处理深向5264车更换后电机动力总成，由于光线昏暗，不慎踩空跌到地沟里，今天医院检查肋骨骨折，需要请几天病假。</t>
-  </si>
-  <si>
-    <t>202507150001</t>
-  </si>
-  <si>
-    <t>张健宁|发起审批|2025-07-15 05:29:15;杜鸣|同意|2025-07-15 14:33:23;罗训强|同意|2025-07-15 14:51:19</t>
-  </si>
-  <si>
-    <t>9h22m3.454s</t>
-  </si>
-  <si>
-    <t>2025年07月15日 05:28</t>
-  </si>
-  <si>
-    <t>2025年07月15日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月15日 下午</t>
-  </si>
-  <si>
-    <t>去医院做定期诊疗。</t>
-  </si>
-  <si>
-    <t>202507140004</t>
-  </si>
-  <si>
-    <t>cafg5ac6</t>
-  </si>
-  <si>
-    <t>陈妍</t>
-  </si>
-  <si>
-    <t>综合保障中心/行政部</t>
-  </si>
-  <si>
-    <t>436fee53c83eb4gf</t>
-  </si>
-  <si>
-    <t>尹娜</t>
-  </si>
-  <si>
-    <t>尹娜;李萍</t>
-  </si>
-  <si>
-    <t>陈妍|发起审批|2025-07-14 08:55:48;尹娜|同意|2025-07-14 09:28:19;李萍|同意|2025-07-14 17:16:03</t>
-  </si>
-  <si>
-    <t>8h20m15.32s</t>
-  </si>
-  <si>
-    <t>2025年07月14日 09:00</t>
-  </si>
-  <si>
-    <t>复查。</t>
-  </si>
-  <si>
-    <t>202507140003</t>
-  </si>
-  <si>
-    <t>c252fg26</t>
-  </si>
-  <si>
-    <t>张喆</t>
-  </si>
-  <si>
-    <t>张喆|发起审批|2025-07-14 08:35:22;林明山|同意|2025-07-14 08:54:03;朱显斌|同意|2025-07-14 09:33:18;雷继彬|同意|2025-07-14 19:10:32</t>
-  </si>
-  <si>
-    <t>10h35m9.814s</t>
-  </si>
-  <si>
-    <t>2025年07月15日 08:30</t>
-  </si>
-  <si>
-    <t>去医院复查</t>
-  </si>
-  <si>
-    <t>202507160003</t>
-  </si>
-  <si>
-    <t>张喆|发起审批|2025-07-16 10:04:41;林明山|同意|2025-07-16 10:15:56;朱显斌|同意|2025-07-16 10:17:25;雷继彬|同意|2025-07-16 10:55:13</t>
-  </si>
-  <si>
-    <t>50m33.083s</t>
-  </si>
-  <si>
-    <t>2025年07月16日 09:57</t>
-  </si>
-  <si>
-    <t>202507150012</t>
-  </si>
-  <si>
-    <t>张喆|发起审批|2025-07-15 12:01:28</t>
-  </si>
-  <si>
-    <t>14m42.803s</t>
-  </si>
-  <si>
-    <t>2025年07月15日 12:00</t>
-  </si>
-  <si>
-    <t>2025年07月16日 上午</t>
-  </si>
-  <si>
-    <t>医院拍片复症</t>
-  </si>
-  <si>
-    <t>202507170003</t>
-  </si>
-  <si>
-    <t>994g1dd6</t>
-  </si>
-  <si>
-    <t>周天</t>
-  </si>
-  <si>
-    <t>周天|发起审批|2025-07-17 09:36:52;张成林|同意|2025-07-17 15:36:15</t>
-  </si>
-  <si>
-    <t>5h59m23.668s</t>
-  </si>
-  <si>
-    <t>2025年07月17日 09:31</t>
-  </si>
-  <si>
-    <t>2025年07月18日 上午</t>
-  </si>
-  <si>
-    <t>6.7调休到7.18</t>
-  </si>
-  <si>
-    <t>202507180008</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-18 11:57:54;张健宁|同意|2025-07-18 12:03:00;杜鸣|同意|2025-07-18 14:02:45;石启军|同意|2025-07-18 14:48:50</t>
-  </si>
-  <si>
-    <t>2h50m55.952s</t>
-  </si>
-  <si>
-    <t>2025年07月18日 11:57</t>
-  </si>
-  <si>
-    <t>202507170011</t>
-  </si>
-  <si>
-    <t>57b3b516</t>
-  </si>
-  <si>
-    <t>韩荣洋</t>
-  </si>
-  <si>
-    <t>韩荣洋|发起审批|2025-07-17 14:57:10;李锋|同意|2025-07-17 15:00:05;张成林|同意|2025-07-17 15:35:07</t>
-  </si>
-  <si>
-    <t>37m57.79s</t>
-  </si>
-  <si>
-    <t>2025年07月17日 14:56</t>
-  </si>
-  <si>
-    <t>私事，需调休一天</t>
-  </si>
-  <si>
-    <t>202507150038</t>
-  </si>
-  <si>
-    <t>5gcg661g</t>
-  </si>
-  <si>
-    <t>丁国涛</t>
-  </si>
-  <si>
-    <t>丁国涛|发起审批|2025-07-15 18:40:12;林明山|同意|2025-07-16 08:43:17;朱显斌|同意|"后补，下次提前走流程" |2025-07-16 08:44:44;雷继彬|同意|2025-07-16 10:55:19</t>
-  </si>
-  <si>
-    <t>16h15m7.944s</t>
-  </si>
-  <si>
-    <t>202507200001</t>
-  </si>
-  <si>
-    <t>d33542g7</t>
-  </si>
-  <si>
-    <t>张斌翌</t>
-  </si>
-  <si>
-    <t>张斌翌|发起审批|2025-07-20 18:18:02;石丁哲|同意|2025-07-21 07:58:27;雷继彬|同意|2025-07-21 09:20:25</t>
-  </si>
-  <si>
-    <t>15h2m23.764s</t>
-  </si>
-  <si>
-    <t>2025年07月20日 18:17</t>
-  </si>
-  <si>
-    <t>2025年07月21日 上午</t>
-  </si>
-  <si>
-    <t>外出办事请半天假</t>
-  </si>
-  <si>
-    <t>202507220028</t>
-  </si>
-  <si>
-    <t>849773g8</t>
-  </si>
-  <si>
-    <t>闫亚东</t>
-  </si>
-  <si>
-    <t>桂治国;朱显斌;雷继彬</t>
-  </si>
-  <si>
-    <t>闫亚东|发起审批|2025-07-22 17:44:43;桂治国|同意|2025-07-22 22:27:42;朱显斌|同意|2025-07-22 22:33:20;雷继彬|同意|2025-07-23 17:11:07</t>
-  </si>
-  <si>
-    <t>23h26m24.454s</t>
-  </si>
-  <si>
-    <t>2025年07月22日 17:42</t>
-  </si>
-  <si>
-    <t>2025年07月26日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月26日 下午</t>
-  </si>
-  <si>
-    <t>家里有事需调休一天。</t>
-  </si>
-  <si>
-    <t>202507220018</t>
-  </si>
-  <si>
-    <t>ca724189</t>
-  </si>
-  <si>
-    <t>邵万江</t>
-  </si>
-  <si>
-    <t>产品中心</t>
-  </si>
-  <si>
-    <t>6dd29dbb8cb19496</t>
-  </si>
-  <si>
-    <t>雷继彬,陈虞涛,石丁哲</t>
-  </si>
-  <si>
-    <t>邵万江|发起审批|2025-07-22 14:39:08;雷继彬|同意|2025-07-22 17:03:28;罗训强|同意|2025-07-22 17:08:53</t>
-  </si>
-  <si>
-    <t>2h29m45.669s</t>
-  </si>
-  <si>
-    <t>2025年07月22日 14:38</t>
-  </si>
-  <si>
-    <t>2025年07月23日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月25日 下午</t>
-  </si>
-  <si>
-    <t>家里有事，回去处理。可远程办公。</t>
-  </si>
-  <si>
-    <t>202507240028</t>
-  </si>
-  <si>
-    <t>周天|发起审批|2025-07-24 17:43:13;张成林|同意|2025-07-24 22:07:13</t>
-  </si>
-  <si>
-    <t>4h24m0.443s</t>
-  </si>
-  <si>
-    <t>2025年07月26日 17:41</t>
-  </si>
-  <si>
-    <t>6.8调休到7.26</t>
-  </si>
-  <si>
-    <t>202507220001</t>
-  </si>
-  <si>
-    <t>fa891163</t>
-  </si>
-  <si>
-    <t>刘小华</t>
-  </si>
-  <si>
-    <t>产品中心/车型开发部</t>
-  </si>
-  <si>
-    <t>c6f869978gf89c59</t>
-  </si>
-  <si>
-    <t>罗锋CDTL</t>
-  </si>
-  <si>
-    <t>罗锋CDTL;雷继彬</t>
-  </si>
-  <si>
-    <t>刘小华|发起审批|2025-07-22 07:06:50;罗锋CDTL|同意|2025-07-24 12:09:35;雷继彬|同意|2025-07-24 14:22:28</t>
-  </si>
-  <si>
-    <t>55h15m38.003s</t>
-  </si>
-  <si>
-    <t>2025年07月22日 07:06</t>
-  </si>
-  <si>
-    <t>2025年07月22日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月22日 下午</t>
-  </si>
-  <si>
-    <t>202507250035</t>
-  </si>
-  <si>
-    <t>吴勇明|发起审批|2025-07-25 17:14:53;张成林|同意|2025-07-25 17:18:47</t>
-  </si>
-  <si>
-    <t>3m54.377s</t>
-  </si>
-  <si>
-    <t>2025年07月25日 17:11</t>
-  </si>
-  <si>
-    <t>调休 5月24调至7月26日休</t>
-  </si>
-  <si>
-    <t>202507250043</t>
-  </si>
-  <si>
-    <t>殷四雄|发起审批|2025-07-25 19:06:58;李锋|同意|2025-07-25 19:07:15;张成林|同意|2025-07-26 09:31:44</t>
-  </si>
-  <si>
-    <t>14h24m46.509s</t>
-  </si>
-  <si>
-    <t>2025年07月25日 19:05</t>
-  </si>
-  <si>
-    <t>累计调休（家里有事）</t>
-  </si>
-  <si>
-    <t>202507240036</t>
-  </si>
-  <si>
-    <t>dad88d24</t>
-  </si>
-  <si>
-    <t>桂治国</t>
-  </si>
-  <si>
-    <t>朱显斌;雷继彬</t>
-  </si>
-  <si>
-    <t>桂治国|发起审批|2025-07-24 22:40:44;朱显斌|同意|2025-07-24 22:41:40;雷继彬|同意|2025-07-24 23:10:02</t>
-  </si>
-  <si>
-    <t>29m18.289s</t>
-  </si>
-  <si>
-    <t>2025年07月24日 22:39</t>
-  </si>
-  <si>
-    <t>父亲重病住院，回家探望。</t>
-  </si>
-  <si>
-    <t>202507250005</t>
-  </si>
-  <si>
-    <t>6aba1885</t>
-  </si>
-  <si>
-    <t>黄风丽</t>
-  </si>
-  <si>
-    <t>供应链管理部</t>
-  </si>
-  <si>
-    <t>a4883fa6f6gc35e4</t>
-  </si>
-  <si>
-    <t>陈虞涛,李萍</t>
-  </si>
-  <si>
-    <t>陈虞涛;罗训强</t>
-  </si>
-  <si>
-    <t>黄风丽|发起审批|2025-07-25 09:18:33;陈虞涛|同意|2025-07-25 11:02:19;罗训强|同意|2025-07-25 12:15:15</t>
-  </si>
-  <si>
-    <t>2h56m42.408s</t>
-  </si>
-  <si>
-    <t>2025年07月25日 14:00</t>
-  </si>
-  <si>
-    <t>医院检查</t>
-  </si>
-  <si>
-    <t>202507250048</t>
-  </si>
-  <si>
-    <t>c617e425</t>
-  </si>
-  <si>
-    <t>李淑娜</t>
-  </si>
-  <si>
-    <t>李淑娜|发起审批|2025-07-25 23:16:49;桂治国|同意|2025-07-25 23:17:21;朱显斌|同意|2025-07-26 00:07:44;雷继彬|同意|2025-07-26 07:47:29</t>
-  </si>
-  <si>
-    <t>8h30m39.786s</t>
-  </si>
-  <si>
-    <t>2025年07月25日 23:07</t>
-  </si>
-  <si>
-    <t>2025年07月31日 上午</t>
-  </si>
-  <si>
-    <t>2025年08月01日 下午</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>我爸妈来杭州了</t>
-  </si>
-  <si>
-    <t>202507260004</t>
-  </si>
-  <si>
-    <t>db4bg33d</t>
-  </si>
-  <si>
-    <t>夏天龙</t>
-  </si>
-  <si>
-    <t>质量保证部/试验科</t>
-  </si>
-  <si>
-    <t>c124dgf868775cfa</t>
-  </si>
-  <si>
-    <t>程志鹏</t>
-  </si>
-  <si>
-    <t>夏天龙|发起审批|2025-07-26 08:57:32</t>
-  </si>
-  <si>
-    <t>6m46.396s</t>
-  </si>
-  <si>
-    <t>2025年07月26日 08:52</t>
-  </si>
-  <si>
-    <t>女朋友父母来杭州，带她们逛逛杭州</t>
-  </si>
-  <si>
-    <t>202507280006</t>
-  </si>
-  <si>
-    <t>陈妍|发起审批|2025-07-28 09:44:48;尹娜|同意|2025-07-28 10:47:52;李萍|同意|2025-07-28 10:53:55</t>
-  </si>
-  <si>
-    <t>1h9m6.711s</t>
-  </si>
-  <si>
-    <t>2025年07月28日 09:40</t>
-  </si>
-  <si>
-    <t>2025年07月29日 上午</t>
-  </si>
-  <si>
-    <t>周二上午复查，中午赶回。</t>
-  </si>
-  <si>
-    <t>202507280001</t>
-  </si>
-  <si>
-    <t>bc269d6g</t>
-  </si>
-  <si>
-    <t>何佳兴</t>
-  </si>
-  <si>
-    <t>何佳兴|发起审批|2025-07-28 00:37:50;林明山|同意|2025-07-28 08:10:23;朱显斌|同意|2025-07-28 08:24:46;雷继彬|同意|2025-07-29 08:39:17</t>
-  </si>
-  <si>
-    <t>32h1m27.509s</t>
-  </si>
-  <si>
-    <t>2025年07月28日 08:30</t>
-  </si>
-  <si>
-    <t>2025年07月28日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月28日 下午</t>
-  </si>
-  <si>
-    <t>各位领导好，周六夜里肠胃炎症状有些严重，虽有药物控制，但周日还是腹泻了一整天，胃里存不下东西，现在特别乏力虚弱，周一申请调休一天，望领导批准。</t>
-  </si>
-  <si>
-    <t>202507250046</t>
-  </si>
-  <si>
-    <t>fb7adb73</t>
-  </si>
-  <si>
-    <t>梁梅</t>
-  </si>
-  <si>
-    <t>张健宁;杜鸣;石启军;李萍;周哲敏</t>
-  </si>
-  <si>
-    <t>梁梅|发起审批|2025-07-25 21:10:10;张健宁|同意|"以加班抵调休，不足部分按事假计算" |2025-07-26 09:02:43;杜鸣|同意|2025-07-28 08:25:01;石启军|同意|2025-07-28 08:26:03;李萍|转交|2025-07-28 10:54:47;周哲敏|同意|2025-07-28 14:23:25</t>
-  </si>
-  <si>
-    <t>65h13m15.72s</t>
-  </si>
-  <si>
-    <t>2025年07月25日 21:07</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>家中婆婆病重</t>
-  </si>
-  <si>
-    <t>202507300001</t>
-  </si>
-  <si>
-    <t>7fe5g917</t>
-  </si>
-  <si>
-    <t>张梓正</t>
-  </si>
-  <si>
-    <t>张梓正|发起审批|2025-07-30 08:11:32;石丁哲|同意|2025-07-30 08:42:54;雷继彬|同意|2025-07-30 08:44:11</t>
-  </si>
-  <si>
-    <t>32m39.391s</t>
-  </si>
-  <si>
-    <t>2025年07月30日 08:11</t>
-  </si>
-  <si>
-    <t>2025年07月30日 上午</t>
-  </si>
-  <si>
-    <t>2025年07月31日 下午</t>
-  </si>
-  <si>
-    <t>202508010002</t>
-  </si>
-  <si>
-    <t>张梓正|发起审批|2025-08-01 09:11:00</t>
-  </si>
-  <si>
-    <t>2025年08月01日 09:10</t>
-  </si>
-  <si>
-    <t>2025年08月01日 上午</t>
-  </si>
-  <si>
-    <t>202507310008</t>
-  </si>
-  <si>
-    <t>朱金凯|发起审批|2025-07-31 10:19:57;张成林|同意|2025-07-31 13:33:46</t>
-  </si>
-  <si>
-    <t>3h13m48.839s</t>
-  </si>
-  <si>
-    <t>2025年07月31日 10:18</t>
-  </si>
-  <si>
-    <t>身体不舒服，阳的症状</t>
-  </si>
-  <si>
-    <t>202508010018</t>
-  </si>
-  <si>
-    <t>陈妍|发起审批|2025-08-01 14:22:56</t>
-  </si>
-  <si>
-    <t>2025年08月01日 14:23</t>
-  </si>
-  <si>
-    <t>2025年08月04日 上午</t>
-  </si>
-  <si>
-    <t>家里有事，周一上午请假半天。</t>
-  </si>
-  <si>
-    <t>202507310031</t>
-  </si>
-  <si>
-    <t>81cgb8bc</t>
-  </si>
-  <si>
-    <t>何升绘</t>
-  </si>
-  <si>
-    <t>陈虞涛</t>
-  </si>
-  <si>
-    <t>何升绘|发起审批|2025-07-31 18:49:04</t>
-  </si>
-  <si>
-    <t>2025年07月31日 18:34</t>
-  </si>
-  <si>
-    <t>2025年08月05日 下午</t>
-  </si>
-  <si>
-    <t>个人私事处理：共3天，调休1天，请假2天</t>
-  </si>
-  <si>
-    <t>202507310016</t>
-  </si>
-  <si>
-    <t>9a282a5e</t>
-  </si>
-  <si>
-    <t>朱泽利</t>
-  </si>
-  <si>
-    <t>朱泽利|发起审批|2025-07-31 14:03:14;石丁哲|同意|2025-08-01 09:14:44;雷继彬|同意|2025-08-01 13:54:14</t>
-  </si>
-  <si>
-    <t>23h51m0.315s</t>
-  </si>
-  <si>
-    <t>2025年08月01日 08:30</t>
-  </si>
-  <si>
-    <t>调休，由加班时间调休到2025年8月1日</t>
-  </si>
-  <si>
-    <t>202507310029</t>
-  </si>
-  <si>
-    <t>c5ddab8a</t>
-  </si>
-  <si>
-    <t>林明山</t>
-  </si>
-  <si>
-    <t>林明山|发起审批|2025-07-31 17:51:21</t>
-  </si>
-  <si>
-    <t>2m42.112s</t>
-  </si>
-  <si>
-    <t>2025年07月31日 17:50</t>
+    <t>甘金利|发起审批|2025-08-28 23:12:06;张成林|同意|2025-08-29 10:03:09</t>
+  </si>
+  <si>
+    <t>10h51m3.072s</t>
+  </si>
+  <si>
+    <t>2025年08月28日 23:09</t>
+  </si>
+  <si>
+    <t>2025年09月01日 上午</t>
+  </si>
+  <si>
+    <t>2025年09月02日 下午</t>
+  </si>
+  <si>
+    <t>七月二十七号和八月三号调休九月一号二号</t>
+  </si>
+  <si>
+    <t>202508270033</t>
+  </si>
+  <si>
+    <t>李锋;张成林;李萍</t>
+  </si>
+  <si>
+    <t>韩荣洋|发起审批|2025-08-27 17:21:31;李锋|同意|"同意" |2025-08-27 17:33:25;张成林|同意|2025-08-27 17:39:12;李萍|同意|2025-08-29 11:38:25</t>
+  </si>
+  <si>
+    <t>42h16m54.11s</t>
+  </si>
+  <si>
+    <t>2025年08月26日 16:20</t>
+  </si>
+  <si>
+    <t>家中急事，调休</t>
+  </si>
+  <si>
+    <t>202508290019</t>
+  </si>
+  <si>
+    <t>闫亚东|发起审批|2025-08-29 10:30:43;桂治国|同意|2025-08-29 12:28:41;朱显斌|同意|2025-08-29 12:29:28;雷继彬|同意|2025-08-29 15:45:32</t>
+  </si>
+  <si>
+    <t>5h14m49.792s</t>
+  </si>
+  <si>
+    <t>2025年08月29日 10:29</t>
+  </si>
+  <si>
+    <t>家里有事需调休半天。</t>
+  </si>
+  <si>
+    <t>202508310001</t>
+  </si>
+  <si>
+    <t>陈妍|发起审批|2025-08-31 09:46:21;尹娜|同意|2025-08-31 20:44:40;李萍|同意|2025-09-01 19:27:22</t>
+  </si>
+  <si>
+    <t>33h41m1.308s</t>
+  </si>
+  <si>
+    <t>2025年09月01日 09:00</t>
+  </si>
+  <si>
+    <t>小孩开学</t>
+  </si>
+  <si>
+    <t>202508310005</t>
+  </si>
+  <si>
+    <t>韩荣洋|发起审批|2025-08-31 20:19:01;李锋|同意|2025-08-31 20:24:26;张成林|同意|2025-08-31 22:01:05</t>
+  </si>
+  <si>
+    <t>1h42m4.787s</t>
+  </si>
+  <si>
+    <t>2025年08月31日 20:16</t>
+  </si>
+  <si>
+    <t>家中急事，请假两天</t>
+  </si>
+  <si>
+    <t>202508310006</t>
+  </si>
+  <si>
+    <t>林明山|发起审批|2025-08-31 22:09:38;朱显斌|同意|2025-08-31 22:32:13;雷继彬|同意|2025-08-31 22:39:09</t>
+  </si>
+  <si>
+    <t>29m31.118s</t>
+  </si>
+  <si>
+    <t>2025年08月31日 22:08</t>
+  </si>
+  <si>
+    <t>2025年09月01日 下午</t>
+  </si>
+  <si>
+    <t>申请调休半天去医院</t>
   </si>
 </sst>
 </file>
@@ -1893,10 +1782,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="1">
-        <v>45840.85733363426</v>
+        <v>45870.38263944445</v>
       </c>
       <c r="E3" s="1">
-        <v>45840.85752648148</v>
+        <v>45870.83076684028</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>40</v>
@@ -1914,49 +1803,49 @@
         <v>44</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>40</v>
@@ -1994,7 +1883,7 @@
     </row>
     <row r="4" ht="20" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>38</v>
@@ -2003,70 +1892,70 @@
         <v>39</v>
       </c>
       <c r="D4" s="1">
-        <v>45850.35340770833</v>
+        <v>45868.34134348379</v>
       </c>
       <c r="E4" s="1">
-        <v>45851.55476037037</v>
+        <v>45868.36402162037</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="O4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="T4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="X4" s="2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>40</v>
@@ -2104,46 +1993,46 @@
     </row>
     <row r="5" ht="20" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="1">
+        <v>45869.784076041666</v>
+      </c>
+      <c r="E5" s="1">
+        <v>45879.842255578704</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D5" s="1">
-        <v>45840.1930962037</v>
-      </c>
-      <c r="E5" s="1">
-        <v>45840.39615453704</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>40</v>
@@ -2155,28 +2044,28 @@
         <v>2</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>40</v>
@@ -2214,79 +2103,79 @@
     </row>
     <row r="6" ht="20" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1">
-        <v>45843.323764849534</v>
+        <v>45869.43053105324</v>
       </c>
       <c r="E6" s="1">
-        <v>45843.68171002315</v>
+        <v>45869.56512409722</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="U6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>3</v>
-      </c>
-      <c r="R6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="Y6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>40</v>
@@ -2324,79 +2213,79 @@
     </row>
     <row r="7" ht="20" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D7" s="1">
-        <v>45842.689578460646</v>
+        <v>45869.74399519676</v>
       </c>
       <c r="E7" s="1">
-        <v>45843.369606099535</v>
+        <v>45869.745871493054</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P7" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>98</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>40</v>
@@ -2440,71 +2329,73 @@
         <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="1">
+        <v>45866.40612053241</v>
+      </c>
+      <c r="E8" s="1">
+        <v>45866.454114872686</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="1">
-        <v>45840.8583830787</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="P8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>40</v>
@@ -2542,46 +2433,46 @@
     </row>
     <row r="9" ht="20" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1">
-        <v>45842.571913252315</v>
+        <v>45869.58558010417</v>
       </c>
       <c r="E9" s="1">
-        <v>45842.78508961805</v>
+        <v>45870.57933375</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>40</v>
@@ -2593,28 +2484,28 @@
         <v>2</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z9" s="2" t="s">
         <v>40</v>
@@ -2652,79 +2543,79 @@
     </row>
     <row r="10" ht="20" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1">
-        <v>45839.63302340278</v>
+        <v>45866.02627565972</v>
       </c>
       <c r="E10" s="1">
-        <v>45840.82803935185</v>
+        <v>45867.3606218287</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>40</v>
@@ -2762,46 +2653,46 @@
     </row>
     <row r="11" ht="20" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1">
-        <v>45845.33596701389</v>
+        <v>45870.59926668982</v>
       </c>
       <c r="E11" s="1">
-        <v>45845.34144519676</v>
+        <v>45874.581762546295</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>40</v>
@@ -2813,28 +2704,28 @@
         <v>2</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>40</v>
@@ -2872,79 +2763,79 @@
     </row>
     <row r="12" ht="20" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1">
-        <v>45843.733441944445</v>
+        <v>45870.71211457176</v>
       </c>
       <c r="E12" s="1">
-        <v>45844.81364903935</v>
+        <v>45871.71482129629</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P12" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="V12" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>40</v>
@@ -2982,79 +2873,79 @@
     </row>
     <row r="13" ht="20" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1">
-        <v>45846.7504478125</v>
+        <v>45871.347640127315</v>
       </c>
       <c r="E13" s="1">
-        <v>45847.053304733796</v>
+        <v>45871.73795418981</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>40</v>
@@ -3092,46 +2983,46 @@
     </row>
     <row r="14" ht="20" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1">
-        <v>45848.445717650466</v>
+        <v>45876.35905208333</v>
       </c>
       <c r="E14" s="1">
-        <v>45848.82117077546</v>
+        <v>45876.589236875</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>40</v>
@@ -3143,28 +3034,28 @@
         <v>3</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>40</v>
@@ -3202,79 +3093,79 @@
     </row>
     <row r="15" ht="20" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1">
-        <v>45846.76119793981</v>
+        <v>45873.306097465276</v>
       </c>
       <c r="E15" s="1">
-        <v>45846.77572369213</v>
+        <v>45873.69370646991</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>40</v>
@@ -3312,40 +3203,40 @@
     </row>
     <row r="16" ht="20" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D16" s="1">
-        <v>45847.32233851852</v>
+        <v>45876.372980451386</v>
       </c>
       <c r="E16" s="1">
-        <v>45847.51561707176</v>
+        <v>45876.42019765046</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>40</v>
@@ -3357,10 +3248,10 @@
         <v>40</v>
       </c>
       <c r="P16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>174</v>
@@ -3369,22 +3260,22 @@
         <v>175</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>176</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>40</v>
@@ -3428,13 +3319,13 @@
         <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D17" s="1">
-        <v>45847.76612480324</v>
+        <v>45875.637136400466</v>
       </c>
       <c r="E17" s="1">
-        <v>45847.78984809028</v>
+        <v>45875.82163118056</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>40</v>
@@ -3446,55 +3337,55 @@
         <v>179</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>40</v>
@@ -3532,79 +3423,79 @@
     </row>
     <row r="18" ht="20" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1">
-        <v>45849.507152592596</v>
+        <v>45874.34294378472</v>
       </c>
       <c r="E18" s="1">
-        <v>45849.50930831018</v>
+        <v>45874.364408877314</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>191</v>
+        <v>93</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P18" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="W18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="X18" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="X18" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="Y18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>40</v>
@@ -3642,46 +3533,46 @@
     </row>
     <row r="19" ht="20" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D19" s="1">
-        <v>45849.67158340278</v>
+        <v>45876.957591087965</v>
       </c>
       <c r="E19" s="1">
-        <v>45849.84621322917</v>
+        <v>45877.34962159722</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="M19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>40</v>
@@ -3693,28 +3584,28 @@
         <v>2</v>
       </c>
       <c r="R19" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U19" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>205</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>40</v>
@@ -3752,46 +3643,46 @@
     </row>
     <row r="20" ht="20" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1">
-        <v>45850.42627913194</v>
+        <v>45877.45243048611</v>
       </c>
       <c r="E20" s="1">
-        <v>45850.65261700231</v>
+        <v>45877.599858657406</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>40</v>
@@ -3803,28 +3694,28 @@
         <v>1</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V20" s="2" t="s">
         <v>205</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>40</v>
@@ -3862,79 +3753,79 @@
     </row>
     <row r="21" ht="20" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D21" s="1">
-        <v>45852.08572311343</v>
+        <v>45877.684300636574</v>
       </c>
       <c r="E21" s="1">
-        <v>45852.30342578704</v>
+        <v>45878.61166149306</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="V21" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X21" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="W21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X21" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="Y21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z21" s="2" t="s">
         <v>40</v>
@@ -3972,40 +3863,40 @@
     </row>
     <row r="22" ht="20" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D22" s="1">
-        <v>45851.55529363426</v>
+        <v>45877.36373341435</v>
       </c>
       <c r="E22" s="1">
-        <v>45852.36244513889</v>
+        <v>45877.47976412037</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>55</v>
+        <v>219</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>59</v>
+        <v>164</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>40</v>
@@ -4017,34 +3908,34 @@
         <v>40</v>
       </c>
       <c r="P22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>222</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>64</v>
+        <v>224</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>225</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>40</v>
@@ -4088,40 +3979,40 @@
         <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D23" s="1">
-        <v>45852.03512447917</v>
+        <v>45877.70264792824</v>
       </c>
       <c r="E23" s="1">
-        <v>45852.65867159722</v>
+        <v>45877.706077916664</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>227</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>108</v>
+        <v>230</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>40</v>
@@ -4133,28 +4024,28 @@
         <v>2</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>40</v>
@@ -4192,79 +4083,79 @@
     </row>
     <row r="24" ht="20" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D24" s="1">
-        <v>45850.847590613426</v>
+        <v>45882.89560790509</v>
       </c>
       <c r="E24" s="1">
-        <v>45852.372705243055</v>
+        <v>45883.371664375</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>232</v>
+        <v>144</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>233</v>
+        <v>145</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>64</v>
+        <v>240</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>224</v>
+        <v>61</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>40</v>
@@ -4302,79 +4193,79 @@
     </row>
     <row r="25" ht="20" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1">
-        <v>45853.228656458334</v>
+        <v>45882.74383171296</v>
       </c>
       <c r="E25" s="1">
-        <v>45853.618974212965</v>
+        <v>45883.704754189814</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>243</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P25" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>51</v>
+        <v>249</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>40</v>
@@ -4412,40 +4303,40 @@
     </row>
     <row r="26" ht="20" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D26" s="1">
-        <v>45852.37209195602</v>
+        <v>45879.61158452546</v>
       </c>
       <c r="E26" s="1">
-        <v>45852.71949149306</v>
+        <v>45879.92317681713</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>251</v>
+        <v>92</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>252</v>
+        <v>93</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>40</v>
@@ -4457,10 +4348,10 @@
         <v>40</v>
       </c>
       <c r="P26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>255</v>
@@ -4469,22 +4360,22 @@
         <v>256</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>40</v>
@@ -4522,79 +4413,79 @@
     </row>
     <row r="27" ht="20" customHeight="true">
       <c r="A27" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D27" s="1">
-        <v>45852.35790099537</v>
+        <v>45878.70384516204</v>
       </c>
       <c r="E27" s="1">
-        <v>45852.79898680555</v>
+        <v>45879.9094727662</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>150</v>
+        <v>263</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>172</v>
+        <v>264</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>151</v>
+        <v>265</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>40</v>
@@ -4632,46 +4523,46 @@
     </row>
     <row r="28" ht="20" customHeight="true">
       <c r="A28" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D28" s="1">
-        <v>45854.41991981481</v>
+        <v>45879.78260883102</v>
       </c>
       <c r="E28" s="1">
-        <v>45854.45502494213</v>
+        <v>45881.36744175926</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>260</v>
+        <v>145</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>40</v>
@@ -4683,28 +4574,28 @@
         <v>3</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>238</v>
+        <v>49</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>40</v>
@@ -4742,7 +4633,7 @@
     </row>
     <row r="29" ht="20" customHeight="true">
       <c r="A29" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>38</v>
@@ -4751,70 +4642,70 @@
         <v>39</v>
       </c>
       <c r="D29" s="1">
-        <v>45853.50101975694</v>
+        <v>45883.83217796296</v>
       </c>
       <c r="E29" s="1">
-        <v>45853.51123738426</v>
+        <v>45884.208924375</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P29" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>238</v>
+        <v>84</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>40</v>
@@ -4852,79 +4743,79 @@
     </row>
     <row r="30" ht="20" customHeight="true">
       <c r="A30" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D30" s="1">
-        <v>45855.40060368056</v>
+        <v>45883.4296219213</v>
       </c>
       <c r="E30" s="1">
-        <v>45855.650183171296</v>
+        <v>45883.62297822917</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>57</v>
+        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>59</v>
+        <v>290</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>65</v>
+        <v>294</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>40</v>
@@ -4962,79 +4853,79 @@
     </row>
     <row r="31" ht="20" customHeight="true">
       <c r="A31" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D31" s="1">
-        <v>45856.498551805555</v>
+        <v>45887.42081739583</v>
       </c>
       <c r="E31" s="1">
-        <v>45856.6172549537</v>
+        <v>45888.49944368056</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>72</v>
+        <v>288</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>63</v>
+        <v>302</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z31" s="2" t="s">
         <v>40</v>
@@ -5072,79 +4963,79 @@
     </row>
     <row r="32" ht="20" customHeight="true">
       <c r="A32" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D32" s="1">
-        <v>45855.62303321759</v>
+        <v>45893.92980298611</v>
       </c>
       <c r="E32" s="1">
-        <v>45855.64939652778</v>
+        <v>45893.97707237268</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>288</v>
+        <v>76</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>40</v>
@@ -5182,79 +5073,79 @@
     </row>
     <row r="33" ht="20" customHeight="true">
       <c r="A33" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D33" s="1">
-        <v>45853.77792021991</v>
+        <v>45889.67862773148</v>
       </c>
       <c r="E33" s="1">
-        <v>45854.45509549769</v>
+        <v>45889.71282487269</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P33" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>204</v>
+        <v>315</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>196</v>
+        <v>316</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>63</v>
+        <v>318</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>40</v>
@@ -5292,79 +5183,79 @@
     </row>
     <row r="34" ht="20" customHeight="true">
       <c r="A34" s="2" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D34" s="1">
-        <v>45858.76252462963</v>
+        <v>45894.92538901621</v>
       </c>
       <c r="E34" s="1">
-        <v>45859.38918856481</v>
+        <v>45895.731404756945</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>40</v>
@@ -5402,46 +5293,46 @@
     </row>
     <row r="35" ht="20" customHeight="true">
       <c r="A35" s="2" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D35" s="1">
-        <v>45860.73939476852</v>
+        <v>45895.97755052083</v>
       </c>
       <c r="E35" s="1">
-        <v>45861.71606668981</v>
+        <v>45896.43198178241</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>308</v>
+        <v>120</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>309</v>
+        <v>121</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>310</v>
+        <v>122</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>40</v>
@@ -5453,28 +5344,28 @@
         <v>3</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>40</v>
@@ -5512,79 +5403,79 @@
     </row>
     <row r="36" ht="20" customHeight="true">
       <c r="A36" s="2" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D36" s="1">
-        <v>45860.610513402775</v>
+        <v>45888.780256226855</v>
       </c>
       <c r="E36" s="1">
-        <v>45860.71451420139</v>
+        <v>45889.31062377315</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>320</v>
+        <v>91</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>321</v>
+        <v>92</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>322</v>
+        <v>93</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>40</v>
@@ -5622,79 +5513,79 @@
     </row>
     <row r="37" ht="20" customHeight="true">
       <c r="A37" s="2" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D37" s="1">
-        <v>45862.73834996528</v>
+        <v>45896.32184341435</v>
       </c>
       <c r="E37" s="1">
-        <v>45862.92168842593</v>
+        <v>45896.432061342595</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>277</v>
+        <v>333</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P37" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>40</v>
@@ -5732,79 +5623,79 @@
     </row>
     <row r="38" ht="20" customHeight="true">
       <c r="A38" s="2" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D38" s="1">
-        <v>45860.2964180787</v>
+        <v>45890.96741613426</v>
       </c>
       <c r="E38" s="1">
-        <v>45862.598941261575</v>
+        <v>45891.452609085645</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>339</v>
+        <v>164</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>40</v>
@@ -5842,79 +5733,79 @@
     </row>
     <row r="39" ht="20" customHeight="true">
       <c r="A39" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1">
-        <v>45863.71867951389</v>
+        <v>45897.58462797454</v>
       </c>
       <c r="E39" s="1">
-        <v>45863.721392210646</v>
+        <v>45897.79562739583</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>138</v>
+        <v>332</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>139</v>
+        <v>333</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P39" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>40</v>
@@ -5952,79 +5843,79 @@
     </row>
     <row r="40" ht="20" customHeight="true">
       <c r="A40" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D40" s="1">
-        <v>45863.79651181713</v>
+        <v>45896.63895712963</v>
       </c>
       <c r="E40" s="1">
-        <v>45864.39705011574</v>
+        <v>45896.676809930555</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>117</v>
+        <v>219</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>118</v>
+        <v>220</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>59</v>
+        <v>164</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>40</v>
@@ -6062,46 +5953,46 @@
     </row>
     <row r="41" ht="20" customHeight="true">
       <c r="A41" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D41" s="1">
-        <v>45862.9449621875</v>
+        <v>45897.37431896991</v>
       </c>
       <c r="E41" s="1">
-        <v>45862.965312754626</v>
+        <v>45897.56743884259</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>357</v>
+        <v>171</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>358</v>
+        <v>172</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>359</v>
+        <v>45</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>40</v>
@@ -6113,28 +6004,28 @@
         <v>2</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>363</v>
+        <v>176</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z41" s="2" t="s">
         <v>40</v>
@@ -6172,46 +6063,46 @@
     </row>
     <row r="42" ht="20" customHeight="true">
       <c r="A42" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D42" s="1">
-        <v>45863.387883379626</v>
+        <v>45896.49719707176</v>
       </c>
       <c r="E42" s="1">
-        <v>45863.51059643518</v>
+        <v>45896.50528525463</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>366</v>
+        <v>114</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>367</v>
+        <v>43</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>368</v>
+        <v>44</v>
       </c>
       <c r="K42" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="M42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>40</v>
@@ -6223,28 +6114,28 @@
         <v>2</v>
       </c>
       <c r="R42" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="S42" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="S42" s="2" t="s">
+      <c r="T42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="X42" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="T42" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="X42" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="Y42" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>40</v>
@@ -6282,40 +6173,40 @@
     </row>
     <row r="43" ht="20" customHeight="true">
       <c r="A43" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D43" s="1">
-        <v>45863.97002296296</v>
+        <v>45896.95379940972</v>
       </c>
       <c r="E43" s="1">
-        <v>45864.32465011574</v>
+        <v>45897.44715388889</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G43" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="I43" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>40</v>
@@ -6327,34 +6218,34 @@
         <v>40</v>
       </c>
       <c r="P43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R43" s="2" t="s">
         <v>379</v>
       </c>
       <c r="S43" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="X43" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T43" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U43" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="V43" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="X43" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="Y43" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>40</v>
@@ -6392,7 +6283,7 @@
     </row>
     <row r="44" ht="20" customHeight="true">
       <c r="A44" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>38</v>
@@ -6401,70 +6292,70 @@
         <v>39</v>
       </c>
       <c r="D44" s="1">
-        <v>45864.37329846065</v>
+        <v>45896.35207519676</v>
       </c>
       <c r="E44" s="1">
-        <v>45864.37800211806</v>
+        <v>45896.43184037037</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P44" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>3</v>
+      </c>
+      <c r="R44" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="S44" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="T44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="X44" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P44" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="2">
-        <v>0</v>
-      </c>
-      <c r="R44" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="S44" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U44" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="X44" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="Y44" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>40</v>
@@ -6502,79 +6393,79 @@
     </row>
     <row r="45" ht="20" customHeight="true">
       <c r="A45" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D45" s="1">
-        <v>45866.40612053241</v>
+        <v>45897.96674134259</v>
       </c>
       <c r="E45" s="1">
-        <v>45866.454114872686</v>
+        <v>45898.41886023148</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N45" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P45" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>1</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="V45" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="O45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P45" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>2</v>
-      </c>
-      <c r="R45" s="2" t="s">
+      <c r="W45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X45" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="S45" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="U45" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="X45" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="Y45" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z45" s="2" t="s">
         <v>40</v>
@@ -6612,46 +6503,46 @@
     </row>
     <row r="46" ht="20" customHeight="true">
       <c r="A46" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D46" s="1">
-        <v>45866.02627565972</v>
+        <v>45896.723280115744</v>
       </c>
       <c r="E46" s="1">
-        <v>45867.3606218287</v>
+        <v>45898.4850175</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>402</v>
+        <v>297</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>403</v>
+        <v>298</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>149</v>
+        <v>288</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>150</v>
+        <v>289</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>151</v>
+        <v>399</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>40</v>
@@ -6663,28 +6554,28 @@
         <v>3</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>407</v>
+        <v>323</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>40</v>
@@ -6722,79 +6613,79 @@
     </row>
     <row r="47" ht="20" customHeight="true">
       <c r="A47" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D47" s="1">
-        <v>45863.88206408565</v>
+        <v>45898.438005462966</v>
       </c>
       <c r="E47" s="1">
-        <v>45866.5996071412</v>
+        <v>45898.656637314816</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>411</v>
+        <v>252</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>412</v>
+        <v>253</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>413</v>
+        <v>193</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P47" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>417</v>
+        <v>85</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>40</v>
@@ -6832,46 +6723,46 @@
     </row>
     <row r="48" ht="20" customHeight="true">
       <c r="A48" s="2" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D48" s="1">
-        <v>45868.34134348379</v>
+        <v>45900.40719048611</v>
       </c>
       <c r="E48" s="1">
-        <v>45868.36402162037</v>
+        <v>45901.81067784722</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>421</v>
+        <v>101</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>40</v>
@@ -6883,28 +6774,28 @@
         <v>2</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>383</v>
+        <v>85</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>185</v>
+        <v>413</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>40</v>
@@ -6942,77 +6833,79 @@
     </row>
     <row r="49" ht="20" customHeight="true">
       <c r="A49" s="2" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="D49" s="1">
-        <v>45870.38263944445</v>
-      </c>
-      <c r="E49" s="1"/>
+        <v>45900.84654104167</v>
+      </c>
+      <c r="E49" s="1">
+        <v>45900.91742978009</v>
+      </c>
       <c r="F49" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>420</v>
+        <v>297</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>421</v>
+        <v>298</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>160</v>
+        <v>288</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>161</v>
+        <v>289</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>40</v>
+        <v>290</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="P49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>40</v>
+        <v>416</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>185</v>
+        <v>418</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z49" s="2" t="s">
         <v>40</v>
@@ -7050,79 +6943,79 @@
     </row>
     <row r="50" ht="20" customHeight="true">
       <c r="A50" s="2" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D50" s="1">
-        <v>45869.43053105324</v>
+        <v>45900.92336709491</v>
       </c>
       <c r="E50" s="1">
-        <v>45869.56512409722</v>
+        <v>45900.94386614583</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>40</v>
@@ -7155,442 +7048,6 @@
         <v>40</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="true">
-      <c r="A51" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D51" s="1">
-        <v>45870.59926668982</v>
-      </c>
-      <c r="E51" s="1"/>
-      <c r="F51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="P51" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U51" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="W51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="X51" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="Y51" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ51" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="true">
-      <c r="A52" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D52" s="1">
-        <v>45869.784076041666</v>
-      </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="O52" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="P52" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S52" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U52" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="W52" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="X52" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="Y52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ52" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="true">
-      <c r="A53" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D53" s="1">
-        <v>45869.58558010417</v>
-      </c>
-      <c r="E53" s="1">
-        <v>45870.57933375</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P53" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q53" s="2">
-        <v>2</v>
-      </c>
-      <c r="R53" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U53" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="W53" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X53" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="Y53" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ53" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="true">
-      <c r="A54" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54" s="1">
-        <v>45869.74399519676</v>
-      </c>
-      <c r="E54" s="1">
-        <v>45869.745871493054</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P54" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="S54" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="T54" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U54" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="V54" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="W54" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="X54" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ54" s="2" t="s">
         <v>40</v>
       </c>
     </row>
